--- a/Basic function/12 most useful excel formulas.xlsx
+++ b/Basic function/12 most useful excel formulas.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="870" firstSheet="9" activeTab="18"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="870" firstSheet="14" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="Vlookup" sheetId="1" r:id="rId1"/>
@@ -31,16 +31,21 @@
     <sheet name="Sheet1" sheetId="17" r:id="rId17"/>
     <sheet name="Sheet2" sheetId="18" r:id="rId18"/>
     <sheet name="Unique" sheetId="19" r:id="rId19"/>
+    <sheet name="Sheet3" sheetId="20" r:id="rId20"/>
+    <sheet name="Sheet5" sheetId="22" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'&amp; Formula'!$B$2:$D$10</definedName>
     <definedName name="abc">_xlfn.XLOOKUP('Picture Lookup'!$F$4,'Picture Lookup'!$B$4:$B$7,'Picture Lookup'!$D$4:$D$7)</definedName>
+    <definedName name="East">Sheet3!$C$3:$C$5</definedName>
+    <definedName name="North">Sheet3!$D$3:$D$4</definedName>
     <definedName name="xyz">_xlfn.XLOOKUP('Picture Lookup'!$F$4,'Picture Lookup'!$B$4:$B$7,'Picture Lookup'!$D$4:$D$7)</definedName>
+    <definedName name="Zone">Sheet3!$B$3:$B$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId20"/>
-    <pivotCache cacheId="4" r:id="rId21"/>
+    <pivotCache cacheId="0" r:id="rId22"/>
+    <pivotCache cacheId="1" r:id="rId23"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -82,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="156">
   <si>
     <t>Product ID</t>
   </si>
@@ -529,6 +534,27 @@
   </si>
   <si>
     <t>age</t>
+  </si>
+  <si>
+    <t>DYNAMIC DEPENDED DROPDOWN LIST</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>West Bengal</t>
+  </si>
+  <si>
+    <t>Jharkhand</t>
+  </si>
+  <si>
+    <t>Bihar</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>UP</t>
   </si>
 </sst>
 </file>
@@ -665,7 +691,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -732,6 +758,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1022,7 +1051,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="abc" spid="_x0000_s4110"/>
+                  <a14:cameraTool cellRange="abc" spid="_x0000_s4120"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1929,58 +1958,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="M4:N8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Units" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="M12:N18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField numFmtId="164" showAll="0"/>
@@ -2038,8 +2016,59 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="M4:N8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="L6:M10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField numFmtId="164" showAll="0"/>
@@ -12208,6 +12237,103 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:G8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8">
+      <formula1>Zone</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8">
+      <formula1>INDIRECT($C$8)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:L32"/>
